--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/84.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/84.xlsx
@@ -426,13 +426,13 @@
         <v>-9.613649671894976</v>
       </c>
       <c r="E2">
-        <v>-7.837454684152728</v>
+        <v>-6.358092795326976</v>
       </c>
       <c r="F2">
-        <v>-5.859621816062968</v>
+        <v>-5.756864496480495</v>
       </c>
       <c r="G2">
-        <v>-5.431030560935659</v>
+        <v>-6.031414547210185</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.648242185936631</v>
       </c>
       <c r="E3">
-        <v>-7.638709016904091</v>
+        <v>-7.059136799506408</v>
       </c>
       <c r="F3">
-        <v>-5.60325370204016</v>
+        <v>-5.733814345130195</v>
       </c>
       <c r="G3">
-        <v>-5.038058873787551</v>
+        <v>-6.064675598243243</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.77680667844777</v>
       </c>
       <c r="E4">
-        <v>-7.776555765697577</v>
+        <v>-7.491587953342897</v>
       </c>
       <c r="F4">
-        <v>-5.694746881679365</v>
+        <v>-5.838314549728159</v>
       </c>
       <c r="G4">
-        <v>-5.053409873453152</v>
+        <v>-6.367908327458326</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.967020172991843</v>
       </c>
       <c r="E5">
-        <v>-9.63479243237507</v>
+        <v>-8.817751566489161</v>
       </c>
       <c r="F5">
-        <v>-5.773841886400871</v>
+        <v>-5.918314131653521</v>
       </c>
       <c r="G5">
-        <v>-5.566779480773474</v>
+        <v>-6.340695643125517</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.18748828819537</v>
       </c>
       <c r="E6">
-        <v>-11.22348979764202</v>
+        <v>-9.561874943903561</v>
       </c>
       <c r="F6">
-        <v>-5.574175521099689</v>
+        <v>-5.45303507211429</v>
       </c>
       <c r="G6">
-        <v>-6.529601992687409</v>
+        <v>-5.745042426426609</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.40605654854756</v>
       </c>
       <c r="E7">
-        <v>-10.54322696068378</v>
+        <v>-10.55472022771525</v>
       </c>
       <c r="F7">
-        <v>-5.213234306147472</v>
+        <v>-5.55349864235841</v>
       </c>
       <c r="G7">
-        <v>-5.825306603026239</v>
+        <v>-6.632139519675256</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.58797223714436</v>
       </c>
       <c r="E8">
-        <v>-12.45087380725897</v>
+        <v>-10.73302889176727</v>
       </c>
       <c r="F8">
-        <v>-5.505015126639958</v>
+        <v>-5.549746138023729</v>
       </c>
       <c r="G8">
-        <v>-6.548280090619977</v>
+        <v>-6.650986455430327</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.7062772054049</v>
       </c>
       <c r="E9">
-        <v>-12.66623897411575</v>
+        <v>-11.4380262537554</v>
       </c>
       <c r="F9">
-        <v>-5.4586605151467</v>
+        <v>-5.263094568489377</v>
       </c>
       <c r="G9">
-        <v>-5.74345005402222</v>
+        <v>-6.553831875489335</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.7451737514718</v>
       </c>
       <c r="E10">
-        <v>-13.50252585453426</v>
+        <v>-11.92240994751185</v>
       </c>
       <c r="F10">
-        <v>-5.374488446613437</v>
+        <v>-5.281568818306611</v>
       </c>
       <c r="G10">
-        <v>-5.174168643089146</v>
+        <v>-6.469032251500904</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.69387061327481</v>
       </c>
       <c r="E11">
-        <v>-13.41975893509607</v>
+        <v>-12.83804474949276</v>
       </c>
       <c r="F11">
-        <v>-4.865607440460451</v>
+        <v>-4.963624013396702</v>
       </c>
       <c r="G11">
-        <v>-5.535514688700597</v>
+        <v>-6.682751139879634</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.55633082378646</v>
       </c>
       <c r="E12">
-        <v>-14.40687569928805</v>
+        <v>-13.75909107791283</v>
       </c>
       <c r="F12">
-        <v>-5.034817221462903</v>
+        <v>-4.81938205428203</v>
       </c>
       <c r="G12">
-        <v>-5.159277809253505</v>
+        <v>-6.520799252098487</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.33702444638322</v>
       </c>
       <c r="E13">
-        <v>-14.96937556967682</v>
+        <v>-15.2372212218085</v>
       </c>
       <c r="F13">
-        <v>-4.739283068268332</v>
+        <v>-4.596399631694251</v>
       </c>
       <c r="G13">
-        <v>-5.515893085289337</v>
+        <v>-6.327959974435941</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.05143786787415</v>
       </c>
       <c r="E14">
-        <v>-16.02878942140126</v>
+        <v>-15.73678888891267</v>
       </c>
       <c r="F14">
-        <v>-4.74555546624233</v>
+        <v>-4.570611726077699</v>
       </c>
       <c r="G14">
-        <v>-5.204430339863625</v>
+        <v>-5.933534957796093</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.721488010607111</v>
       </c>
       <c r="E15">
-        <v>-17.423717912354</v>
+        <v>-17.07117168238285</v>
       </c>
       <c r="F15">
-        <v>-4.524279480504317</v>
+        <v>-4.414466127384798</v>
       </c>
       <c r="G15">
-        <v>-4.289246578259801</v>
+        <v>-5.551014662915464</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.36693153293807</v>
       </c>
       <c r="E16">
-        <v>-17.38234124534592</v>
+        <v>-17.30354579761245</v>
       </c>
       <c r="F16">
-        <v>-4.149589023400433</v>
+        <v>-3.651340941229781</v>
       </c>
       <c r="G16">
-        <v>-4.434678843799984</v>
+        <v>-5.550574360358741</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.015592801023443</v>
       </c>
       <c r="E17">
-        <v>-19.6704297217795</v>
+        <v>-18.49495108123846</v>
       </c>
       <c r="F17">
-        <v>-4.075886690471153</v>
+        <v>-3.672306091827234</v>
       </c>
       <c r="G17">
-        <v>-4.123752406751635</v>
+        <v>-5.125586387300342</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.699606037397936</v>
       </c>
       <c r="E18">
-        <v>-20.01478394227076</v>
+        <v>-19.11750757391695</v>
       </c>
       <c r="F18">
-        <v>-3.800509201288902</v>
+        <v>-3.27839088403918</v>
       </c>
       <c r="G18">
-        <v>-4.449390908176506</v>
+        <v>-5.059673425613453</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.446877822695749</v>
       </c>
       <c r="E19">
-        <v>-20.25347075026705</v>
+        <v>-19.6954042559318</v>
       </c>
       <c r="F19">
-        <v>-3.390744011615682</v>
+        <v>-2.927434809760308</v>
       </c>
       <c r="G19">
-        <v>-4.235463455428802</v>
+        <v>-4.778018832223339</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.285657193066726</v>
       </c>
       <c r="E20">
-        <v>-20.35137182983888</v>
+        <v>-21.03801981514793</v>
       </c>
       <c r="F20">
-        <v>-3.138952627493341</v>
+        <v>-2.304292117534768</v>
       </c>
       <c r="G20">
-        <v>-4.046047281853862</v>
+        <v>-5.778713985106537</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.226689614270146</v>
       </c>
       <c r="E21">
-        <v>-22.00046998142013</v>
+        <v>-21.82778568208564</v>
       </c>
       <c r="F21">
-        <v>-2.699193910899557</v>
+        <v>-2.426477137815098</v>
       </c>
       <c r="G21">
-        <v>-3.679232215011535</v>
+        <v>-5.135508092281538</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.273982207992166</v>
       </c>
       <c r="E22">
-        <v>-22.4378073587109</v>
+        <v>-21.46140496402106</v>
       </c>
       <c r="F22">
-        <v>-2.453820717414107</v>
+        <v>-2.073826223830098</v>
       </c>
       <c r="G22">
-        <v>-4.704720043438336</v>
+        <v>-5.059709841614384</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.416387949594931</v>
       </c>
       <c r="E23">
-        <v>-23.14799435191182</v>
+        <v>-23.1629836008772</v>
       </c>
       <c r="F23">
-        <v>-2.42145640298673</v>
+        <v>-1.702713485538905</v>
       </c>
       <c r="G23">
-        <v>-3.783954702055301</v>
+        <v>-5.629239543462903</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.620660523059053</v>
       </c>
       <c r="E24">
-        <v>-24.0625513770789</v>
+        <v>-23.2110352385726</v>
       </c>
       <c r="F24">
-        <v>-2.160148734141029</v>
+        <v>-1.517051499549452</v>
       </c>
       <c r="G24">
-        <v>-4.098873657024011</v>
+        <v>-4.600788776778455</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.848804329343691</v>
       </c>
       <c r="E25">
-        <v>-22.60097280568127</v>
+        <v>-23.98751909124581</v>
       </c>
       <c r="F25">
-        <v>-1.966641280479662</v>
+        <v>-1.577847039975714</v>
       </c>
       <c r="G25">
-        <v>-4.580038277338303</v>
+        <v>-5.390135391889042</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.053967588040448</v>
       </c>
       <c r="E26">
-        <v>-24.25472622854241</v>
+        <v>-24.12961807713249</v>
       </c>
       <c r="F26">
-        <v>-1.560182105111014</v>
+        <v>-1.241088354613422</v>
       </c>
       <c r="G26">
-        <v>-4.120494829940991</v>
+        <v>-5.22152930757396</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.188235209823684</v>
       </c>
       <c r="E27">
-        <v>-23.79552537874261</v>
+        <v>-23.19884005806994</v>
       </c>
       <c r="F27">
-        <v>-1.644790723265553</v>
+        <v>-1.22246085682667</v>
       </c>
       <c r="G27">
-        <v>-5.329294185968316</v>
+        <v>-5.18251121784811</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.211473865069248</v>
       </c>
       <c r="E28">
-        <v>-24.56440592355694</v>
+        <v>-23.29709435861436</v>
       </c>
       <c r="F28">
-        <v>-1.734964313632099</v>
+        <v>-1.39510836255074</v>
       </c>
       <c r="G28">
-        <v>-4.930578702309573</v>
+        <v>-5.5249606695214</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.085404621787177</v>
       </c>
       <c r="E29">
-        <v>-23.84913798251942</v>
+        <v>-23.39509959308836</v>
       </c>
       <c r="F29">
-        <v>-1.788070119458172</v>
+        <v>-1.406692252311488</v>
       </c>
       <c r="G29">
-        <v>-4.620956620203696</v>
+        <v>-5.645431421695479</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.792870601059853</v>
       </c>
       <c r="E30">
-        <v>-23.77511101791603</v>
+        <v>-22.88681914199343</v>
       </c>
       <c r="F30">
-        <v>-1.848429938630561</v>
+        <v>-1.421331989421164</v>
       </c>
       <c r="G30">
-        <v>-5.544353845290451</v>
+        <v>-5.781892108824237</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.328043045071189</v>
       </c>
       <c r="E31">
-        <v>-24.11313896021858</v>
+        <v>-22.51983160841183</v>
       </c>
       <c r="F31">
-        <v>-1.90533960757029</v>
+        <v>-1.592833863027162</v>
       </c>
       <c r="G31">
-        <v>-4.904580988189676</v>
+        <v>-5.333766732991871</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.698809852129346</v>
       </c>
       <c r="E32">
-        <v>-22.63961427438872</v>
+        <v>-22.81293256008428</v>
       </c>
       <c r="F32">
-        <v>-1.837797014648227</v>
+        <v>-1.71800680452939</v>
       </c>
       <c r="G32">
-        <v>-4.268396762453471</v>
+        <v>-5.700558626015423</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.933412066192807</v>
       </c>
       <c r="E33">
-        <v>-22.80926449613807</v>
+        <v>-22.96570515920705</v>
       </c>
       <c r="F33">
-        <v>-1.866699581699304</v>
+        <v>-1.791867355632605</v>
       </c>
       <c r="G33">
-        <v>-4.606436567468452</v>
+        <v>-5.661027401730985</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.064395631782212</v>
       </c>
       <c r="E34">
-        <v>-22.55870402929367</v>
+        <v>-21.85706679501924</v>
       </c>
       <c r="F34">
-        <v>-2.103492545626557</v>
+        <v>-1.79640183879553</v>
       </c>
       <c r="G34">
-        <v>-4.786172705886564</v>
+        <v>-4.957235214991784</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.134959812737953</v>
       </c>
       <c r="E35">
-        <v>-22.80641155751324</v>
+        <v>-21.11368155886808</v>
       </c>
       <c r="F35">
-        <v>-2.13322513681524</v>
+        <v>-1.907054328094085</v>
       </c>
       <c r="G35">
-        <v>-4.176502639374382</v>
+        <v>-5.348396033729911</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.190104541122237</v>
       </c>
       <c r="E36">
-        <v>-20.15022607136618</v>
+        <v>-21.0077152670886</v>
       </c>
       <c r="F36">
-        <v>-2.278219253531654</v>
+        <v>-1.888155954166617</v>
       </c>
       <c r="G36">
-        <v>-4.34953161252993</v>
+        <v>-4.767577371592477</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.265035944832541</v>
       </c>
       <c r="E37">
-        <v>-21.40585870184297</v>
+        <v>-20.44801852211058</v>
       </c>
       <c r="F37">
-        <v>-2.210267447112607</v>
+        <v>-1.765256052817671</v>
       </c>
       <c r="G37">
-        <v>-4.225899289365847</v>
+        <v>-4.520481563086815</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.400021495552377</v>
       </c>
       <c r="E38">
-        <v>-20.6420319340212</v>
+        <v>-20.60299648807508</v>
       </c>
       <c r="F38">
-        <v>-2.163887984597266</v>
+        <v>-2.014998884352889</v>
       </c>
       <c r="G38">
-        <v>-3.039730822644981</v>
+        <v>-4.336862154751139</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.622707862073931</v>
       </c>
       <c r="E39">
-        <v>-21.14668054896198</v>
+        <v>-20.19962266584184</v>
       </c>
       <c r="F39">
-        <v>-2.008709090663432</v>
+        <v>-2.21965699162334</v>
       </c>
       <c r="G39">
-        <v>-4.211183914443787</v>
+        <v>-3.683972916223772</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9523424471117065</v>
       </c>
       <c r="E40">
-        <v>-20.76618004894148</v>
+        <v>-19.80554580074635</v>
       </c>
       <c r="F40">
-        <v>-2.044325575514199</v>
+        <v>-2.534727361645535</v>
       </c>
       <c r="G40">
-        <v>-2.888660698051419</v>
+        <v>-4.000848403606192</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.4047595851175812</v>
       </c>
       <c r="E41">
-        <v>-19.74407176609223</v>
+        <v>-19.06542106588073</v>
       </c>
       <c r="F41">
-        <v>-2.081221059634889</v>
+        <v>-2.224372887247478</v>
       </c>
       <c r="G41">
-        <v>-3.467112320128273</v>
+        <v>-3.511698747451177</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.02085967316087467</v>
       </c>
       <c r="E42">
-        <v>-18.84502476440142</v>
+        <v>-17.9000997925389</v>
       </c>
       <c r="F42">
-        <v>-2.016789814677741</v>
+        <v>-2.194064580713849</v>
       </c>
       <c r="G42">
-        <v>-3.180174096057482</v>
+        <v>-3.734541499336139</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.3286027253681341</v>
       </c>
       <c r="E43">
-        <v>-18.11099535555012</v>
+        <v>-18.31160675408991</v>
       </c>
       <c r="F43">
-        <v>-2.788472036103677</v>
+        <v>-2.317829297631318</v>
       </c>
       <c r="G43">
-        <v>-2.765819595271222</v>
+        <v>-3.301763812623835</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.52984313828424</v>
       </c>
       <c r="E44">
-        <v>-17.67748906726984</v>
+        <v>-16.43383425054333</v>
       </c>
       <c r="F44">
-        <v>-2.569667898695618</v>
+        <v>-2.31773237864519</v>
       </c>
       <c r="G44">
-        <v>-2.820499875943364</v>
+        <v>-3.037320745492391</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.6436905836963159</v>
       </c>
       <c r="E45">
-        <v>-16.9403712391453</v>
+        <v>-16.71211350678868</v>
       </c>
       <c r="F45">
-        <v>-2.420768029675004</v>
+        <v>-2.271651956762259</v>
       </c>
       <c r="G45">
-        <v>-2.781587723674771</v>
+        <v>-2.9791379076397</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.6840172821555537</v>
       </c>
       <c r="E46">
-        <v>-17.61026387062597</v>
+        <v>-16.36624677597885</v>
       </c>
       <c r="F46">
-        <v>-2.585157540760566</v>
+        <v>-2.383740835137269</v>
       </c>
       <c r="G46">
-        <v>-2.818874398083582</v>
+        <v>-2.405185316950715</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.6658551277769048</v>
       </c>
       <c r="E47">
-        <v>-16.99752510959611</v>
+        <v>-15.54549708988066</v>
       </c>
       <c r="F47">
-        <v>-2.281454028239586</v>
+        <v>-2.450389619631711</v>
       </c>
       <c r="G47">
-        <v>-1.924828469748005</v>
+        <v>-2.452724750894649</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.6011390081832058</v>
       </c>
       <c r="E48">
-        <v>-15.89508169785079</v>
+        <v>-14.77469647208707</v>
       </c>
       <c r="F48">
-        <v>-2.634179495290838</v>
+        <v>-2.650744358244619</v>
       </c>
       <c r="G48">
-        <v>-2.490978104600928</v>
+        <v>-2.639813610955482</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.497383516069926</v>
       </c>
       <c r="E49">
-        <v>-14.55265633454298</v>
+        <v>-14.77060726005815</v>
       </c>
       <c r="F49">
-        <v>-2.559947007223765</v>
+        <v>-2.475330933762601</v>
       </c>
       <c r="G49">
-        <v>-2.388682247437449</v>
+        <v>-2.504657278769197</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.3584359908176305</v>
       </c>
       <c r="E50">
-        <v>-14.35297327317475</v>
+        <v>-13.30243975897935</v>
       </c>
       <c r="F50">
-        <v>-2.586585646162992</v>
+        <v>-2.991475065303334</v>
       </c>
       <c r="G50">
-        <v>-2.18440503493672</v>
+        <v>-2.484628478256606</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.1845911193747252</v>
       </c>
       <c r="E51">
-        <v>-14.44613756893456</v>
+        <v>-13.59365686546462</v>
       </c>
       <c r="F51">
-        <v>-2.517218159852562</v>
+        <v>-2.812340614447941</v>
       </c>
       <c r="G51">
-        <v>-3.363144637467462</v>
+        <v>-2.102677597208732</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.02803865240229694</v>
       </c>
       <c r="E52">
-        <v>-14.46914674536753</v>
+        <v>-12.70031574102347</v>
       </c>
       <c r="F52">
-        <v>-2.976788939619102</v>
+        <v>-2.784419662769181</v>
       </c>
       <c r="G52">
-        <v>-2.948475634854971</v>
+        <v>-2.209333442847432</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.2849199339788989</v>
       </c>
       <c r="E53">
-        <v>-14.3078923144284</v>
+        <v>-12.25937822689661</v>
       </c>
       <c r="F53">
-        <v>-3.209409416938453</v>
+        <v>-2.74526604910846</v>
       </c>
       <c r="G53">
-        <v>-1.672392751287499</v>
+        <v>-2.685307127756147</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.5870040484340906</v>
       </c>
       <c r="E54">
-        <v>-13.35038271329856</v>
+        <v>-11.51506918204789</v>
       </c>
       <c r="F54">
-        <v>-2.641083937593172</v>
+        <v>-2.909648933254799</v>
       </c>
       <c r="G54">
-        <v>-2.179819929364829</v>
+        <v>-1.980045058797509</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.9381103974768632</v>
       </c>
       <c r="E55">
-        <v>-12.0804265195355</v>
+        <v>-11.08420299411409</v>
       </c>
       <c r="F55">
-        <v>-2.978456443200937</v>
+        <v>-2.816100574089248</v>
       </c>
       <c r="G55">
-        <v>-2.480500227969135</v>
+        <v>-2.044163704802114</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.337304487896691</v>
       </c>
       <c r="E56">
-        <v>-12.15568975754298</v>
+        <v>-10.40205178349466</v>
       </c>
       <c r="F56">
-        <v>-2.927908635914709</v>
+        <v>-2.964365085311915</v>
       </c>
       <c r="G56">
-        <v>-2.236268041354942</v>
+        <v>-1.946982640496808</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.780829428994824</v>
       </c>
       <c r="E57">
-        <v>-11.77556964933913</v>
+        <v>-10.80172584246363</v>
       </c>
       <c r="F57">
-        <v>-3.222499278637491</v>
+        <v>-3.079396324701668</v>
       </c>
       <c r="G57">
-        <v>-3.105892075247315</v>
+        <v>-2.288273401231353</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.266711510282159</v>
       </c>
       <c r="E58">
-        <v>-11.12445659956827</v>
+        <v>-9.950658022884085</v>
       </c>
       <c r="F58">
-        <v>-3.00027978242769</v>
+        <v>-3.042516579561632</v>
       </c>
       <c r="G58">
-        <v>-3.440700787815968</v>
+        <v>-2.277818698418335</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.783097649695736</v>
       </c>
       <c r="E59">
-        <v>-11.75626929311844</v>
+        <v>-9.380980521193163</v>
       </c>
       <c r="F59">
-        <v>-3.277926998293612</v>
+        <v>-3.12895091947194</v>
       </c>
       <c r="G59">
-        <v>-2.790211694804572</v>
+        <v>-2.360539299808104</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.318466729059115</v>
       </c>
       <c r="E60">
-        <v>-9.375627864916096</v>
+        <v>-9.568721996603159</v>
       </c>
       <c r="F60">
-        <v>-2.953979843183018</v>
+        <v>-2.906664325502513</v>
       </c>
       <c r="G60">
-        <v>-2.895884308418109</v>
+        <v>-2.087485503729017</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.859322568015341</v>
       </c>
       <c r="E61">
-        <v>-10.55915813224277</v>
+        <v>-8.303996190318959</v>
       </c>
       <c r="F61">
-        <v>-3.748494355332316</v>
+        <v>-2.902608638698406</v>
       </c>
       <c r="G61">
-        <v>-2.997455156108488</v>
+        <v>-2.678762179225008</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.387409373179356</v>
       </c>
       <c r="E62">
-        <v>-9.485266749115802</v>
+        <v>-7.904621010634495</v>
       </c>
       <c r="F62">
-        <v>-2.848179930130062</v>
+        <v>-2.740312412039719</v>
       </c>
       <c r="G62">
-        <v>-2.77995562472391</v>
+        <v>-2.351339293754469</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.893003802935872</v>
       </c>
       <c r="E63">
-        <v>-10.19119697674951</v>
+        <v>-8.081630002646314</v>
       </c>
       <c r="F63">
-        <v>-3.103674944910319</v>
+        <v>-2.961739160645041</v>
       </c>
       <c r="G63">
-        <v>-3.651095888473269</v>
+        <v>-2.911255171356944</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.362666127076458</v>
       </c>
       <c r="E64">
-        <v>-9.65180138074788</v>
+        <v>-7.557558762686639</v>
       </c>
       <c r="F64">
-        <v>-3.012893332870118</v>
+        <v>-2.986276231483365</v>
       </c>
       <c r="G64">
-        <v>-2.738967760402193</v>
+        <v>-2.71495306306032</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.785835568576116</v>
       </c>
       <c r="E65">
-        <v>-8.698208909634678</v>
+        <v>-8.630204815461493</v>
       </c>
       <c r="F65">
-        <v>-3.269885207547234</v>
+        <v>-3.024283384658612</v>
       </c>
       <c r="G65">
-        <v>-3.688667269798458</v>
+        <v>-2.924656259699914</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.157531766286431</v>
       </c>
       <c r="E66">
-        <v>-10.03437139338988</v>
+        <v>-8.196952121725648</v>
       </c>
       <c r="F66">
-        <v>-3.488183212472182</v>
+        <v>-2.724290958102173</v>
       </c>
       <c r="G66">
-        <v>-3.449109573485717</v>
+        <v>-2.87861319233973</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.470621037690299</v>
       </c>
       <c r="E67">
-        <v>-9.258077736624989</v>
+        <v>-7.138942096943583</v>
       </c>
       <c r="F67">
-        <v>-3.008331513582902</v>
+        <v>-3.038131202531211</v>
       </c>
       <c r="G67">
-        <v>-3.691573928781938</v>
+        <v>-2.487584795423175</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.72392937388007</v>
       </c>
       <c r="E68">
-        <v>-9.177339573542234</v>
+        <v>-7.751794069823635</v>
       </c>
       <c r="F68">
-        <v>-3.291376371445465</v>
+        <v>-3.118083567514613</v>
       </c>
       <c r="G68">
-        <v>-2.866784613127915</v>
+        <v>-2.271005595698515</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.913858142094308</v>
       </c>
       <c r="E69">
-        <v>-9.814509451843476</v>
+        <v>-7.183239629686614</v>
       </c>
       <c r="F69">
-        <v>-3.45023653011734</v>
+        <v>-3.331865313359499</v>
       </c>
       <c r="G69">
-        <v>-3.534339568394253</v>
+        <v>-2.23187494742433</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.035094098736239</v>
       </c>
       <c r="E70">
-        <v>-8.394561141998357</v>
+        <v>-7.677961829602578</v>
       </c>
       <c r="F70">
-        <v>-3.395478131322681</v>
+        <v>-3.273602920450998</v>
       </c>
       <c r="G70">
-        <v>-3.65536318167339</v>
+        <v>-2.641164313535505</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.084701864454765</v>
       </c>
       <c r="E71">
-        <v>-9.103226567932701</v>
+        <v>-7.21775113009907</v>
       </c>
       <c r="F71">
-        <v>-3.426689358325361</v>
+        <v>-3.316552113551347</v>
       </c>
       <c r="G71">
-        <v>-3.156804955095767</v>
+        <v>-2.563300282451846</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.055644221144965</v>
       </c>
       <c r="E72">
-        <v>-9.82713483737686</v>
+        <v>-7.172366763594198</v>
       </c>
       <c r="F72">
-        <v>-3.545969294124073</v>
+        <v>-3.516683192965499</v>
       </c>
       <c r="G72">
-        <v>-3.44300823805684</v>
+        <v>-2.633990361351904</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.944610954491888</v>
       </c>
       <c r="E73">
-        <v>-9.612100249122633</v>
+        <v>-7.207611876795896</v>
       </c>
       <c r="F73">
-        <v>-3.393334316484236</v>
+        <v>-3.518887478624349</v>
       </c>
       <c r="G73">
-        <v>-3.93489902591837</v>
+        <v>-3.15320308154904</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.74817529107612</v>
       </c>
       <c r="E74">
-        <v>-10.33646589444157</v>
+        <v>-7.545888885168872</v>
       </c>
       <c r="F74">
-        <v>-3.462673638302971</v>
+        <v>-3.457207241811898</v>
       </c>
       <c r="G74">
-        <v>-2.436754679213205</v>
+        <v>-2.311847796016504</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.468623941488185</v>
       </c>
       <c r="E75">
-        <v>-10.47798523565528</v>
+        <v>-7.883473037018674</v>
       </c>
       <c r="F75">
-        <v>-3.579291201269086</v>
+        <v>-3.556512754426905</v>
       </c>
       <c r="G75">
-        <v>-2.187751996476923</v>
+        <v>-1.110242255446016</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.116294412636964</v>
       </c>
       <c r="E76">
-        <v>-9.142411453521072</v>
+        <v>-7.771166881628449</v>
       </c>
       <c r="F76">
-        <v>-3.912686714976011</v>
+        <v>-3.693991093697719</v>
       </c>
       <c r="G76">
-        <v>-2.522474634861554</v>
+        <v>-1.115813903588609</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.704020343631021</v>
       </c>
       <c r="E77">
-        <v>-9.72786163018071</v>
+        <v>-8.552518843859907</v>
       </c>
       <c r="F77">
-        <v>-3.62957724445603</v>
+        <v>-3.822932278515282</v>
       </c>
       <c r="G77">
-        <v>-1.523136805649457</v>
+        <v>-1.203063331276101</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.253264809671623</v>
       </c>
       <c r="E78">
-        <v>-10.42016567952534</v>
+        <v>-8.776239045260846</v>
       </c>
       <c r="F78">
-        <v>-3.907443149316291</v>
+        <v>-3.892996421811467</v>
       </c>
       <c r="G78">
-        <v>-1.652370571865987</v>
+        <v>-1.057680723919007</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.788382496375528</v>
       </c>
       <c r="E79">
-        <v>-12.44381844475502</v>
+        <v>-9.197803747582896</v>
       </c>
       <c r="F79">
-        <v>-4.2036988105187</v>
+        <v>-3.968078814833811</v>
       </c>
       <c r="G79">
-        <v>-1.298261378803383</v>
+        <v>-0.1318072107688769</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.334007555525603</v>
       </c>
       <c r="E80">
-        <v>-11.27313998666211</v>
+        <v>-9.469186137914566</v>
       </c>
       <c r="F80">
-        <v>-4.155271623783638</v>
+        <v>-4.378835560288183</v>
       </c>
       <c r="G80">
-        <v>-2.111132730516031</v>
+        <v>-0.06404034357999576</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.91843115802672</v>
       </c>
       <c r="E81">
-        <v>-12.16825627291427</v>
+        <v>-10.20684285444601</v>
       </c>
       <c r="F81">
-        <v>-4.536628781745252</v>
+        <v>-4.366682582121711</v>
       </c>
       <c r="G81">
-        <v>-0.8179376370560661</v>
+        <v>-0.1019593321868079</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.564381184692451</v>
       </c>
       <c r="E82">
-        <v>-13.89826014111656</v>
+        <v>-11.01239951024847</v>
       </c>
       <c r="F82">
-        <v>-4.427722490931798</v>
+        <v>-4.719934890841143</v>
       </c>
       <c r="G82">
-        <v>-1.086297079560467</v>
+        <v>0.3939305946861624</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.293182402455593</v>
       </c>
       <c r="E83">
-        <v>-12.87380610873133</v>
+        <v>-11.98118954013141</v>
       </c>
       <c r="F83">
-        <v>-4.570188430334869</v>
+        <v>-4.929129966376728</v>
       </c>
       <c r="G83">
-        <v>-0.6632159807326879</v>
+        <v>0.6251523373310193</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.122857243366996</v>
       </c>
       <c r="E84">
-        <v>-13.98071912432223</v>
+        <v>-13.39760111177654</v>
       </c>
       <c r="F84">
-        <v>-4.787139509862865</v>
+        <v>-4.94186611519477</v>
       </c>
       <c r="G84">
-        <v>-0.3400140408247205</v>
+        <v>0.9691378821345312</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.061611142731858</v>
       </c>
       <c r="E85">
-        <v>-15.11479845548514</v>
+        <v>-13.93084251160175</v>
       </c>
       <c r="F85">
-        <v>-5.009402909545014</v>
+        <v>-5.332915171769138</v>
       </c>
       <c r="G85">
-        <v>0.4143930766643977</v>
+        <v>0.9562830338055411</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.112669423183491</v>
       </c>
       <c r="E86">
-        <v>-16.19512932865101</v>
+        <v>-14.54120382377758</v>
       </c>
       <c r="F86">
-        <v>-4.92656202742805</v>
+        <v>-5.544734515236792</v>
       </c>
       <c r="G86">
-        <v>0.1400878943714656</v>
+        <v>1.748241669346612</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.277900005755428</v>
       </c>
       <c r="E87">
-        <v>-17.85904011871135</v>
+        <v>-16.29796191641719</v>
       </c>
       <c r="F87">
-        <v>-5.269685887913452</v>
+        <v>-5.621995514528499</v>
       </c>
       <c r="G87">
-        <v>0.5478941360810475</v>
+        <v>1.519214818394292</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.549961831700723</v>
       </c>
       <c r="E88">
-        <v>-18.8166719886394</v>
+        <v>-17.57860078036434</v>
       </c>
       <c r="F88">
-        <v>-5.45664509725569</v>
+        <v>-5.930747926369542</v>
       </c>
       <c r="G88">
-        <v>0.532175665860588</v>
+        <v>1.234683360930552</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.921415074590735</v>
       </c>
       <c r="E89">
-        <v>-20.33138767404303</v>
+        <v>-19.05786304276193</v>
       </c>
       <c r="F89">
-        <v>-5.878703259186454</v>
+        <v>-5.938030104207552</v>
       </c>
       <c r="G89">
-        <v>0.2815375736279057</v>
+        <v>1.613929526272841</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.382009329739753</v>
       </c>
       <c r="E90">
-        <v>-22.45802699515514</v>
+        <v>-19.73139203887075</v>
       </c>
       <c r="F90">
-        <v>-6.011821900816335</v>
+        <v>-6.157902007197819</v>
       </c>
       <c r="G90">
-        <v>-0.1896589940676409</v>
+        <v>2.09783196774811</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.916503864366232</v>
       </c>
       <c r="E91">
-        <v>-24.60158922363392</v>
+        <v>-21.75125899983002</v>
       </c>
       <c r="F91">
-        <v>-5.583993331557669</v>
+        <v>-6.396195558675243</v>
       </c>
       <c r="G91">
-        <v>0.1196254123932304</v>
+        <v>1.377295041671276</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.51308336737524</v>
       </c>
       <c r="E92">
-        <v>-26.26880579971986</v>
+        <v>-24.35381376830424</v>
       </c>
       <c r="F92">
-        <v>-6.067808768469345</v>
+        <v>-6.773185149505597</v>
       </c>
       <c r="G92">
-        <v>-0.0926103515839061</v>
+        <v>1.459681277961579</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.154246586462981</v>
       </c>
       <c r="E93">
-        <v>-27.80394490289809</v>
+        <v>-25.59222461212987</v>
       </c>
       <c r="F93">
-        <v>-5.972681541034058</v>
+        <v>-6.675099822074913</v>
       </c>
       <c r="G93">
-        <v>-0.5681702183002121</v>
+        <v>0.8687720730204466</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.816991308911385</v>
       </c>
       <c r="E94">
-        <v>-30.31446749411443</v>
+        <v>-28.3593848823089</v>
       </c>
       <c r="F94">
-        <v>-6.232717665916462</v>
+        <v>-7.154519113179933</v>
       </c>
       <c r="G94">
-        <v>-1.346664865133067</v>
+        <v>0.9179038793687703</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.485484597545068</v>
       </c>
       <c r="E95">
-        <v>-31.99737070416294</v>
+        <v>-30.54396149987515</v>
       </c>
       <c r="F95">
-        <v>-6.620051080505573</v>
+        <v>-7.291632142426113</v>
       </c>
       <c r="G95">
-        <v>-1.329102421047234</v>
+        <v>0.1012982322878251</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.133625805704458</v>
       </c>
       <c r="E96">
-        <v>-33.61339514582917</v>
+        <v>-32.70829583862712</v>
       </c>
       <c r="F96">
-        <v>-6.443253868277179</v>
+        <v>-7.225598420728248</v>
       </c>
       <c r="G96">
-        <v>-1.911794851959895</v>
+        <v>-0.1040218020577739</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.739054933331872</v>
       </c>
       <c r="E97">
-        <v>-36.39555145768461</v>
+        <v>-35.19363332164979</v>
       </c>
       <c r="F97">
-        <v>-6.566690551703139</v>
+        <v>-7.679528432665426</v>
       </c>
       <c r="G97">
-        <v>-1.962125075793435</v>
+        <v>-0.1563747692158084</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.281638238239022</v>
       </c>
       <c r="E98">
-        <v>-39.17244341850613</v>
+        <v>-37.23822122221693</v>
       </c>
       <c r="F98">
-        <v>-6.611156485518014</v>
+        <v>-7.610034206142367</v>
       </c>
       <c r="G98">
-        <v>-3.447371537077599</v>
+        <v>-1.377883309568395</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.738683574570059</v>
       </c>
       <c r="E99">
-        <v>-41.67947455626256</v>
+        <v>-40.37612992364094</v>
       </c>
       <c r="F99">
-        <v>-7.0327474482336</v>
+        <v>-7.917995527113736</v>
       </c>
       <c r="G99">
-        <v>-3.054661383027094</v>
+        <v>-2.338418234514694</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.0995820589796</v>
       </c>
       <c r="E100">
-        <v>-44.07660868680083</v>
+        <v>-42.49096351301505</v>
       </c>
       <c r="F100">
-        <v>-6.879393447688133</v>
+        <v>-7.678369132485208</v>
       </c>
       <c r="G100">
-        <v>-4.21593785783818</v>
+        <v>-3.150538092389927</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.35230870884902</v>
       </c>
       <c r="E101">
-        <v>-45.66686384712641</v>
+        <v>-45.30883816360599</v>
       </c>
       <c r="F101">
-        <v>-7.047271213906884</v>
+        <v>-8.015139414991138</v>
       </c>
       <c r="G101">
-        <v>-5.177138202437873</v>
+        <v>-3.45191029501194</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.49003415673721</v>
       </c>
       <c r="E102">
-        <v>-49.1686716628588</v>
+        <v>-47.10142101412028</v>
       </c>
       <c r="F102">
-        <v>-7.107703101043316</v>
+        <v>-8.081754650605768</v>
       </c>
       <c r="G102">
-        <v>-5.649473597798929</v>
+        <v>-4.597981434161154</v>
       </c>
     </row>
   </sheetData>
